--- a/docs/etl2/数据导入核验清单.xlsx
+++ b/docs/etl2/数据导入核验清单.xlsx
@@ -1,215 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25500" windowHeight="12420"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25500" windowHeight="12420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>医院名称</t>
-  </si>
-  <si>
-    <t>数据项名称</t>
-  </si>
-  <si>
-    <t>数据存放目录</t>
-  </si>
-  <si>
-    <t>预期记录数</t>
-  </si>
-  <si>
-    <t>完成状态</t>
-  </si>
-  <si>
-    <t>核验结果文件存放路径</t>
-  </si>
-  <si>
-    <t>省医</t>
-  </si>
-  <si>
-    <t>CT影像(含报告)</t>
-  </si>
-  <si>
-    <t>/data/wlx/DATABASE/extracted_tables/shengyi/CT_image/*06*.parquet
-/data/wlx/DATABASE/extracted_tables/shengyi/CT_image/*07*.parquet</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -509,161 +471,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -717,11 +680,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -981,55 +1007,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="18.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="67.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="22.1818181818182" customWidth="1"/>
-    <col min="5" max="5" width="14.7272727272727" customWidth="1"/>
-    <col min="6" max="6" width="28.8181818181818" customWidth="1"/>
+    <col width="26" customWidth="1" style="2" min="1" max="1"/>
+    <col width="18.8181818181818" customWidth="1" style="2" min="2" max="2"/>
+    <col width="67.5454545454545" customWidth="1" style="2" min="3" max="3"/>
+    <col width="22.1818181818182" customWidth="1" style="2" min="4" max="4"/>
+    <col width="14.7272727272727" customWidth="1" style="2" min="5" max="5"/>
+    <col width="28.8181818181818" customWidth="1" style="2" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>医院名称</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>数据项名称</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>数据存放目录</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>预期记录数</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>完成状态</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>核验结果文件存放路径</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="56" spans="1:4">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+    <row r="2" ht="56" customHeight="1" s="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>省医</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>CT影像(含报告)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>/data/wlx/DATABASE/extracted_tables/shengyi/CT_image/*06*.parquet
+/data/wlx/DATABASE/extracted_tables/shengyi/CT_image/*07*.parquet</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>82994</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>未完成（源数据 82,994 行与清单预期一致，但 ETL2 spec 与离线灌库脚本未覆盖 shengyi CT_image；PG lnrs_anon_imaging_study shengyi=0；详见 verify_result/shengyi_CT_image_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_CT_image_20260914.md</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/etl2/数据导入核验清单.xlsx
+++ b/docs/etl2/数据导入核验清单.xlsx
@@ -1075,14 +1075,14 @@
       <c r="D2" s="0" t="n">
         <v>82994</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>未完成（源数据 82,994 行与清单预期一致，但 ETL2 spec 与离线灌库脚本未覆盖 shengyi CT_image；PG lnrs_anon_imaging_study shengyi=0；详见 verify_result/shengyi_CT_image_20260914.md）</t>
+          <t>已完成（影像 +82,994 行落 PG [unique 82,153]；patient 增量 +82,682；详见 verify_result/shengyi_CT_image_20260914_after_import.md）</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>docs/etl2/verify_result/shengyi_CT_image_20260914.md</t>
+          <t>docs/etl2/verify_result/shengyi_CT_image_20260914_after_import.md</t>
         </is>
       </c>
     </row>

--- a/docs/etl2/数据导入核验清单.xlsx
+++ b/docs/etl2/数据导入核验清单.xlsx
@@ -1210,8 +1210,16 @@
       <c r="D6" s="0" t="n">
         <v>1359243</v>
       </c>
-      <c r="E6" s="0" t="n"/>
-      <c r="F6" s="0" t="n"/>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>🟡 部分通过（数据本体完整，但首页.诊断 1,000,030 → PG 520,104 hash 撞键；详见 verify_result/shengyi_discharge_summary_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_discharge_summary_20260914.md</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">

--- a/docs/etl2/数据导入核验清单.xlsx
+++ b/docs/etl2/数据导入核验清单.xlsx
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>🟡 部分通过（数据本体完整，但首页.诊断 1,000,030 → PG 520,104 hash 撞键；详见 verify_result/shengyi_discharge_summary_20260914.md）</t>
+          <t>✅ 已完成（方案 B3 已实施；surgery 324,637 + 首页诊断 988,058；SHA256 抽样 200/200 命中；FK 0 孤儿；详见 verify_result/shengyi_discharge_summary_20260914.md）</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">

--- a/docs/etl2/数据导入核验清单.xlsx
+++ b/docs/etl2/数据导入核验清单.xlsx
@@ -1240,8 +1240,16 @@
       <c r="D7" s="0" t="n">
         <v>515585</v>
       </c>
-      <c r="E7" s="0" t="n"/>
-      <c r="F7" s="0" t="n"/>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（staging 515,585 行 → PG 515,485 行 imaging 4 类 + 100 行 hash 被前置 spec 占用；SHA256 抽样 200/200 命中；FK 0 孤儿；详见 verify_result/shengyi_imaging_report_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_imaging_report_20260914.md</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -1262,8 +1270,16 @@
       <c r="D8" s="0" t="n">
         <v>2381102</v>
       </c>
-      <c r="E8" s="0" t="n"/>
-      <c r="F8" s="0" t="n"/>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 2,381,102 → staging 2,381,010 → PG visit+visit_detail 各 2,381,010；staging hash 100% 命中；FK 0 孤儿；visit↔visit_detail 1:1；详见 verify_result/shengyi_visit_record_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_visit_record_20260914.md</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">

--- a/docs/etl2/数据导入核验清单.xlsx
+++ b/docs/etl2/数据导入核验清单.xlsx
@@ -632,7 +632,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -645,6 +645,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1300,8 +1303,16 @@
       <c r="D9" s="0" t="n">
         <v>4925535</v>
       </c>
-      <c r="E9" s="0" t="n"/>
-      <c r="F9" s="0" t="n"/>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 4,925,535 行 = 清单预期；ETL2 hash 去重 308,266 行业务键冗余；PG lnrs_anon_diagnosis(source=diagnosis) 4,617,269 行；staging→PG hash 4,617,269/4,617,269 全命中；FK 0 孤儿；详见 verify_result/shengyi_diagnosis_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_diagnosis_20260914.md</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -1322,10 +1333,18 @@
       <c r="D10" s="0" t="n">
         <v>2456529</v>
       </c>
-      <c r="E10" s="0" t="n"/>
-      <c r="F10" s="0" t="n"/>
-    </row>
-    <row r="11">
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 2,456,529 → ETL1 staging 2,456,529 → ETL2 batch 56ec3bef-b33c-4233-a5a2-d41f99e9637a (2026-09-02 20:39:37→21:01:25) 写入 PG lnrs_anon_order 2,456,529 行；FK 0 孤儿；hash 0 重复；staging hash 5000/5000 命中；详见 verify_result/shengyi_outp_order_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_outp_order_20260914.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="1">
       <c r="A11" s="0" t="inlineStr">
         <is>
           <t>省医</t>
@@ -1344,8 +1363,16 @@
       <c r="D11" s="4" t="n">
         <v>24689334</v>
       </c>
-      <c r="E11" s="0" t="n"/>
-      <c r="F11" s="0" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 24,689,334 = drug 11,402,839 + no_drug 13,286,495；ETL1 staging 24,689,328；ETL2 hash 去重后 17,597,075；PG lnrs_anon_order drug_order 段 6,967,742 + no_drug_order 段 10,629,344 = 17,597,086；5000/5000 抽样命中；FK 0 孤儿；source_order_hash 0 重复；batch b6bd60ba/80ec80db；详见 verify_result/shengyi_inpatient_order_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_inpatient_order_20260914.md</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -1366,8 +1393,16 @@
       <c r="D12" s="0" t="n">
         <v>44096008</v>
       </c>
-      <c r="E12" s="0" t="n"/>
-      <c r="F12" s="0" t="n"/>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 44,096,008 → ETL1 staging 4 片 44,096,008 → ETL2 引擎 imported 43,952,198；PG lnrs_anon_lab_result shengyi 实测 44,952,193；4 批 staging hash 各 500/500 抽样命中；FK 0 孤儿；source_lab_hash 100% 唯一；详见 verify_result/shengyi_lab_result_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_lab_result_20260914.md</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -1388,8 +1423,16 @@
       <c r="D13" s="0" t="n">
         <v>1557086</v>
       </c>
-      <c r="E13" s="0" t="n"/>
-      <c r="F13" s="0" t="n"/>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 1,557,086 行 = 1,557,086 sub_items → ETL1 staging 聚合 181,605 份报告；staging→PG 181,604 命中 / 1 行 exam_date='' 引擎守卫过滤；PG lnrs_anon_exam(Ultrasound) 181,691 = 181,604 + 87 from_other；FK 0 孤儿；SHA256 抽样 200/200 命中；详见 verify_result/shengyi_ultrasound_20260914.md）</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_ultrasound_20260914.md</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -1410,8 +1453,16 @@
       <c r="D14" s="0" t="n">
         <v>1740013</v>
       </c>
-      <c r="E14" s="0" t="n"/>
-      <c r="F14" s="0" t="n"/>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 1,740,013 行 = 1,740,013 sub_items → ETL1 staging 聚合 149,072 份报告；staging→PG 149,072 命中 / 0 miss；PG lnrs_anon_exam(ECG) 149,072 = 149,072 (本 R14 staging) + 0 from_other；FK 0 孤儿；source_exam_hash 0 重复；report_text 148,848 / 224 no_text = 224 行 staging ecg_diagnosis 空被 ETL2 body 跳过；详见 verify_result/shengyi_ecg_20260915.md）</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_ecg_20260915.md</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -1432,8 +1483,16 @@
       <c r="D15" s="0" t="n">
         <v>1403598</v>
       </c>
-      <c r="E15" s="0" t="n"/>
-      <c r="F15" s="0" t="n"/>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 1,403,598 行 → ETL1 staging 1,403,598（0 守卫过滤）→ ETL2 引擎守卫+去重后 699,536 → PG lnrs_anon_medical_history shengyi 699,536；200 抽样 200/200 命中；FK 0 孤儿；source_hist_hash 全局 0 重复；6 个 data_source；record_date 范围 2005-03-06 ~ 2025-11-06；详见 verify_result/shengyi_medical_history_20260915.md）</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_medical_history_20260915.md</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -1454,8 +1513,16 @@
       <c r="D16" s="0" t="n">
         <v>5164052</v>
       </c>
-      <c r="E16" s="0" t="n"/>
-      <c r="F16" s="0" t="n"/>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（源 5,164,052 → ETL1 staging 5,164,052（0 守卫过滤）→ ETL2 引擎去重后 2,672,861 = PG lnrs_anon_clinical_document shengyi 全量；staging hash → PG 2,672,861/2,672,861 = 100% 命中；PG 反向覆盖 2,672,861/2,672,861 = 100%；200 抽样 200/200 ✅；FK 0 孤儿；source_doc_hash 全局 0 重复；uniq_patient staging 78,594 = PG 78,594 完全一致；batch d56e9cf1-1dbd-4dbc-8034-a55a3efbb541，2026-09-04 02:41:49 完成；详见 verify_result/shengyi_clinical_document_20260915.md）</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_clinical_document_20260915.md</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">

--- a/docs/etl2/数据导入核验清单.xlsx
+++ b/docs/etl2/数据导入核验清单.xlsx
@@ -1543,8 +1543,16 @@
       <c r="D17" s="0" t="n">
         <v>87138</v>
       </c>
-      <c r="E17" s="0" t="n"/>
-      <c r="F17" s="0" t="n"/>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>🟡 部分通过（数据已落库 87,132 行 PG [import_R1 batch=5207cce4];PG ⊆ staging 100% 反向覆盖;但 staging 后期追加 6 个 patient_id (1000583033/1000585649/3452897/3175462/458900/2967004) ETL2 patient 路径未再重跑;需用户决策路径 A/B/C;详见 verify_result/shengyi_patient_20260915.md）</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_patient_20260915.md</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -1565,8 +1573,16 @@
       <c r="D18" s="0" t="n">
         <v>78384</v>
       </c>
-      <c r="E18" s="0" t="n"/>
-      <c r="F18" s="0" t="n"/>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>🟡 部分通过（数据已落库 324,637 行 PG [batch=3429fa10 R3 import]; PG ⊆ staging 100% 反向覆盖; source_surgery_hash 100% 唯一; 200 抽样 100% 命中; 0 FK 孤儿; PHI 审计 324,639 行; 但 staging 与 PG 在 hash 集合上 1.05% 不对称差异(3,419 行), 全部源自 staging procedure_name 字段被 ETL 日志污染(\n[INFO] ... preparing : ...), 并非数据丢失;详见 verify_result/shengyi_surgery_20260915.md）</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_surgery_20260915.md</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -1587,8 +1603,16 @@
       <c r="D19" s="0" t="n">
         <v>3326029</v>
       </c>
-      <c r="E19" s="0" t="n"/>
-      <c r="F19" s="0" t="n"/>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（2 个 ETL2 spec 全部对账；源 3,326,029 行 = 清单预期; anesthesia_observation → PG lnrs_anon_vital_observation 2,957,408 行 [R15 batch=2367dd54, source_locator=import_R15]; anesthesia_order → PG lnrs_anon_order 323,945 行 [R10 batch=56ec3bef, source_locator=import_R10, 与 outp_order 共用]; 守卫过滤 8,580 + 去重 36,096 = 44,676; staging ⊆ PG 100%; 200 抽样 200/200 = 100%; hash 唯一性 100%; FK patient_id 0 孤儿; 详见 verify_result/shengyi_anesthesia_20260915.md）</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_anesthesia_20260915.md</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
@@ -1609,8 +1633,16 @@
       <c r="D20" s="0" t="n">
         <v>16736346</v>
       </c>
-      <c r="E20" s="0" t="n"/>
-      <c r="F20" s="0" t="n"/>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>🟡 部分通过（数据已 100% 落库。源 glob 合计 16,736,346 = 护理记录.测量子项 13,824,664 + ICU护理记录 2,911,682 = 清单 R20 预期; ETL2 两个 spec 全部对账; nursing_observation → PG lnrs_anon_vital_observation(obs_type=nursing) 11,666,186 行 [R14 batch=64735062, source_locator=import_R14]; icu_observation → PG lnrs_anon_vital_observation(obs_type=icu) 1,679,556 行 [R15 batch=2367dd54, source_locator=import_R15, 与 anesthesia_observation 共用]; 守卫过滤 13,412 + 去重 3,377,192 = 3,390,604 行差异均为 ETL2 引擎合法去重, 无数据丢失; staging ⊆ PG 100%; 200 抽样 nursing 200/200 + icu 200/200 = 100%; hash 唯一性 100%; FK patient_id 0 孤儿; 注意: import_R14 第一批 batch(99704778) nursing 跑出 0 行(success 但空, 3 分钟后立即 re-run 成功); nursing obs_time = -infinity 哨兵 1 行(ETL2 解析失败保留); 详见 verify_result/shengyi_nursing_20260915.md）</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>docs/etl2/verify_result/shengyi_nursing_20260915.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
